--- a/organization-server/src/main/resources/Import_template.xlsx
+++ b/organization-server/src/main/resources/Import_template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="154">
   <si>
     <t>填表说明：
 1. 千万不要修改表结构，只能填写下面空格和增加行数，不要删除此说明行和表头行，不要删除列和新加列；
@@ -38,8 +38,9 @@
 6. 性别：请填写男或女；
 7. 人员类型：请从下列选项中选填一个选项：“正式“、“实习“、“外包“、“劳务“、“顾问“，若不填则默认为“正式“；
 8. 部门负责人：请填入“是“、“否“，若不填则默认为“否“，若归属于多个部门请用英文“,”隔开；
-9. 入职时间：请按YYYY-MM-DD的格式填写，如2022-01-01； -10. 下面数据为示例和测试数据，实际使用时请删除从第三行（包含第三行）开始的数据，填上实际公司数据。</t>
+9. 入职时间：请按YYYY-MM-DD的格式填写，如2022-01-01；
+10. 高管模式：请填入“是“、“否“，若不填则默认为“否“。开启高管模式后，该成员的手机号、邮箱、分机号、工位、城市、工号只有管理后台、本人和其他高管可以查看，其他人在客户端通讯录中看不到这些信息； +11. 下面数据为示例和测试数据，实际使用时请删除从第三行（包含第三行）开始的数据，填上实际公司数据。</t>
   </si>
   <si>
     <t>用户ID</t>
@@ -496,6 +497,9 @@
   </si>
   <si>
     <t>2022-01-31</t>
+  </si>
+  <si>
+    <t>高管模式（是/否）</t>
   </si>
 </sst>
 </file>
@@ -2443,7 +2447,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
@@ -2459,10 +2463,11 @@
     <col min="11" max="13" width="12.675" style="1" customWidth="1"/>
     <col min="14" max="15" width="16" style="1" customWidth="1"/>
     <col min="16" max="16" width="15.55" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="17" max="17" width="15.55" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="205.55" customHeight="1" spans="1:16">
+    <row r="1" ht="205.55" customHeight="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2481,8 +2486,9 @@
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
     </row>
-    <row r="2" ht="19.25" customHeight="1" spans="1:16">
+    <row r="2" ht="19.25" customHeight="1" spans="1:17">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -2531,8 +2537,11 @@
       <c r="P2" s="8" t="s">
         <v>16</v>
       </c>
+      <c r="Q2" s="8" t="s">
+        <v>153</v>
+      </c>
     </row>
-    <row r="3" ht="16.75" customHeight="1" spans="1:16">
+    <row r="3" ht="16.75" customHeight="1" spans="1:17">
       <c r="A3" s="9"/>
       <c r="B3" s="10" t="s">
         <v>17</v>
@@ -2575,8 +2584,11 @@
       <c r="P3" s="15">
         <v>123456</v>
       </c>
+      <c r="Q3" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="4" ht="17" customHeight="1" spans="1:16">
+    <row r="4" ht="17" customHeight="1" spans="1:17">
       <c r="A4" s="16"/>
       <c r="B4" s="17" t="s">
         <v>26</v>
@@ -2619,8 +2631,11 @@
       <c r="P4" s="15">
         <v>123456</v>
       </c>
+      <c r="Q4" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="5" ht="17" customHeight="1" spans="1:16">
+    <row r="5" ht="17" customHeight="1" spans="1:17">
       <c r="A5" s="16"/>
       <c r="B5" s="17" t="s">
         <v>33</v>
@@ -2663,8 +2678,11 @@
       <c r="P5" s="15">
         <v>123456</v>
       </c>
+      <c r="Q5" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="6" ht="17" customHeight="1" spans="1:16">
+    <row r="6" ht="17" customHeight="1" spans="1:17">
       <c r="A6" s="16"/>
       <c r="B6" s="17" t="s">
         <v>39</v>
@@ -2707,8 +2725,11 @@
       <c r="P6" s="15">
         <v>123456</v>
       </c>
+      <c r="Q6" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="7" ht="17" customHeight="1" spans="1:16">
+    <row r="7" ht="17" customHeight="1" spans="1:17">
       <c r="A7" s="16"/>
       <c r="B7" s="17" t="s">
         <v>45</v>
@@ -2751,8 +2772,11 @@
       <c r="P7" s="15">
         <v>123456</v>
       </c>
+      <c r="Q7" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="8" ht="17" customHeight="1" spans="1:16">
+    <row r="8" ht="17" customHeight="1" spans="1:17">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>51</v>
@@ -2793,8 +2817,11 @@
       <c r="P8" s="15">
         <v>123456</v>
       </c>
+      <c r="Q8" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="9" ht="17" customHeight="1" spans="1:16">
+    <row r="9" ht="17" customHeight="1" spans="1:17">
       <c r="A9" s="16"/>
       <c r="B9" s="17" t="s">
         <v>57</v>
@@ -2835,8 +2862,11 @@
       <c r="P9" s="15">
         <v>123456</v>
       </c>
+      <c r="Q9" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="10" ht="17" customHeight="1" spans="1:16">
+    <row r="10" ht="17" customHeight="1" spans="1:17">
       <c r="A10" s="16"/>
       <c r="B10" s="17" t="s">
         <v>62</v>
@@ -2877,8 +2907,11 @@
       <c r="P10" s="15">
         <v>123456</v>
       </c>
+      <c r="Q10" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="11" ht="17" customHeight="1" spans="1:16">
+    <row r="11" ht="17" customHeight="1" spans="1:17">
       <c r="A11" s="16"/>
       <c r="B11" s="17" t="s">
         <v>67</v>
@@ -2919,8 +2952,11 @@
       <c r="P11" s="15">
         <v>123456</v>
       </c>
+      <c r="Q11" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="12" ht="17" customHeight="1" spans="1:16">
+    <row r="12" ht="17" customHeight="1" spans="1:17">
       <c r="A12" s="16"/>
       <c r="B12" s="17" t="s">
         <v>72</v>
@@ -2961,8 +2997,11 @@
       <c r="P12" s="15">
         <v>123456</v>
       </c>
+      <c r="Q12" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="13" ht="17" customHeight="1" spans="1:16">
+    <row r="13" ht="17" customHeight="1" spans="1:17">
       <c r="A13" s="16"/>
       <c r="B13" s="17" t="s">
         <v>77</v>
@@ -3003,8 +3042,11 @@
       <c r="P13" s="15">
         <v>123456</v>
       </c>
+      <c r="Q13" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="14" ht="17" customHeight="1" spans="1:16">
+    <row r="14" ht="17" customHeight="1" spans="1:17">
       <c r="A14" s="16"/>
       <c r="B14" s="17" t="s">
         <v>82</v>
@@ -3045,8 +3087,11 @@
       <c r="P14" s="15">
         <v>123456</v>
       </c>
+      <c r="Q14" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="15" ht="17" customHeight="1" spans="1:16">
+    <row r="15" ht="17" customHeight="1" spans="1:17">
       <c r="A15" s="16"/>
       <c r="B15" s="17" t="s">
         <v>86</v>
@@ -3087,8 +3132,11 @@
       <c r="P15" s="15">
         <v>123456</v>
       </c>
+      <c r="Q15" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="16" ht="17" customHeight="1" spans="1:16">
+    <row r="16" ht="17" customHeight="1" spans="1:17">
       <c r="A16" s="16"/>
       <c r="B16" s="17" t="s">
         <v>90</v>
@@ -3129,8 +3177,11 @@
       <c r="P16" s="15">
         <v>123456</v>
       </c>
+      <c r="Q16" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="17" ht="17" customHeight="1" spans="1:16">
+    <row r="17" ht="17" customHeight="1" spans="1:17">
       <c r="A17" s="16"/>
       <c r="B17" s="17" t="s">
         <v>95</v>
@@ -3171,8 +3222,11 @@
       <c r="P17" s="15">
         <v>123456</v>
       </c>
+      <c r="Q17" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="18" ht="17" customHeight="1" spans="1:16">
+    <row r="18" ht="17" customHeight="1" spans="1:17">
       <c r="A18" s="16"/>
       <c r="B18" s="17" t="s">
         <v>99</v>
@@ -3213,8 +3267,11 @@
       <c r="P18" s="15">
         <v>123456</v>
       </c>
+      <c r="Q18" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="19" ht="17" customHeight="1" spans="1:16">
+    <row r="19" ht="17" customHeight="1" spans="1:17">
       <c r="A19" s="16"/>
       <c r="B19" s="17" t="s">
         <v>104</v>
@@ -3255,8 +3312,11 @@
       <c r="P19" s="15">
         <v>123456</v>
       </c>
+      <c r="Q19" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="20" ht="17" customHeight="1" spans="1:16">
+    <row r="20" ht="17" customHeight="1" spans="1:17">
       <c r="A20" s="16"/>
       <c r="B20" s="17" t="s">
         <v>108</v>
@@ -3297,8 +3357,11 @@
       <c r="P20" s="15">
         <v>123456</v>
       </c>
+      <c r="Q20" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="21" ht="17" customHeight="1" spans="1:16">
+    <row r="21" ht="17" customHeight="1" spans="1:17">
       <c r="A21" s="16"/>
       <c r="B21" s="17" t="s">
         <v>113</v>
@@ -3339,8 +3402,11 @@
       <c r="P21" s="15">
         <v>123456</v>
       </c>
+      <c r="Q21" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="22" ht="17" customHeight="1" spans="1:16">
+    <row r="22" ht="17" customHeight="1" spans="1:17">
       <c r="A22" s="16"/>
       <c r="B22" s="17" t="s">
         <v>116</v>
@@ -3381,8 +3447,11 @@
       <c r="P22" s="15">
         <v>123456</v>
       </c>
+      <c r="Q22" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="23" ht="17" customHeight="1" spans="1:16">
+    <row r="23" ht="17" customHeight="1" spans="1:17">
       <c r="A23" s="16"/>
       <c r="B23" s="17" t="s">
         <v>119</v>
@@ -3423,8 +3492,11 @@
       <c r="P23" s="15">
         <v>123456</v>
       </c>
+      <c r="Q23" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="24" ht="17" customHeight="1" spans="1:16">
+    <row r="24" ht="17" customHeight="1" spans="1:17">
       <c r="A24" s="16"/>
       <c r="B24" s="17" t="s">
         <v>122</v>
@@ -3465,8 +3537,11 @@
       <c r="P24" s="15">
         <v>123456</v>
       </c>
+      <c r="Q24" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="25" ht="17" customHeight="1" spans="1:16">
+    <row r="25" ht="17" customHeight="1" spans="1:17">
       <c r="A25" s="16"/>
       <c r="B25" s="17" t="s">
         <v>125</v>
@@ -3507,8 +3582,11 @@
       <c r="P25" s="15">
         <v>123456</v>
       </c>
+      <c r="Q25" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="26" ht="17" customHeight="1" spans="1:16">
+    <row r="26" ht="17" customHeight="1" spans="1:17">
       <c r="A26" s="16"/>
       <c r="B26" s="17" t="s">
         <v>128</v>
@@ -3549,8 +3627,11 @@
       <c r="P26" s="15">
         <v>123456</v>
       </c>
+      <c r="Q26" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="27" ht="17" customHeight="1" spans="1:16">
+    <row r="27" ht="17" customHeight="1" spans="1:17">
       <c r="A27" s="16"/>
       <c r="B27" s="17" t="s">
         <v>132</v>
@@ -3591,8 +3672,11 @@
       <c r="P27" s="15">
         <v>123456</v>
       </c>
+      <c r="Q27" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="28" ht="17" customHeight="1" spans="1:16">
+    <row r="28" ht="17" customHeight="1" spans="1:17">
       <c r="A28" s="16"/>
       <c r="B28" s="17" t="s">
         <v>135</v>
@@ -3633,8 +3717,11 @@
       <c r="P28" s="15">
         <v>123456</v>
       </c>
+      <c r="Q28" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="29" ht="17" customHeight="1" spans="1:16">
+    <row r="29" ht="17" customHeight="1" spans="1:17">
       <c r="A29" s="16"/>
       <c r="B29" s="17" t="s">
         <v>138</v>
@@ -3675,8 +3762,11 @@
       <c r="P29" s="15">
         <v>123456</v>
       </c>
+      <c r="Q29" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="30" ht="17" customHeight="1" spans="1:16">
+    <row r="30" ht="17" customHeight="1" spans="1:17">
       <c r="A30" s="16"/>
       <c r="B30" s="17" t="s">
         <v>141</v>
@@ -3717,8 +3807,11 @@
       <c r="P30" s="15">
         <v>123456</v>
       </c>
+      <c r="Q30" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="31" ht="17" customHeight="1" spans="1:16">
+    <row r="31" ht="17" customHeight="1" spans="1:17">
       <c r="A31" s="16"/>
       <c r="B31" s="17" t="s">
         <v>144</v>
@@ -3759,8 +3852,11 @@
       <c r="P31" s="15">
         <v>123456</v>
       </c>
+      <c r="Q31" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="32" ht="17" customHeight="1" spans="1:16">
+    <row r="32" ht="17" customHeight="1" spans="1:17">
       <c r="A32" s="16"/>
       <c r="B32" s="17" t="s">
         <v>147</v>
@@ -3801,8 +3897,11 @@
       <c r="P32" s="15">
         <v>123456</v>
       </c>
+      <c r="Q32" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="33" ht="17" customHeight="1" spans="1:16">
+    <row r="33" ht="17" customHeight="1" spans="1:17">
       <c r="A33" s="16"/>
       <c r="B33" s="17" t="s">
         <v>150</v>
@@ -3843,10 +3942,13 @@
       <c r="P33" s="15">
         <v>123456</v>
       </c>
+      <c r="Q33" s="15" t="s">
+        <v>111</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <pageMargins left="0.699306" right="0.699306" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
